--- a/output/2026-09-05_11_Italia_Sicilia_Cleaning.xlsx
+++ b/output/2026-09-05_11_Italia_Sicilia_Cleaning.xlsx
@@ -485,7 +485,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Filiale del gruppo PerPulire S.r.l. (sede legale Roma), attivo in Sicilia con filiali a Palermo e Messina. Macchine pulizia industriale, spazzatrici, lavasciuga, ingrosso prodotti pulizia. Indirizzo esatto filiale, telefono ed email non reperiti con certezza.</t>
+          <t>Filiale del gruppo PerPulire S.r.l. (sede legale Roma), attivo in Sicilia con filiali a Palermo e Messina. Macchine pulizia industriale, spazzatrici, lavasciuga, ingrosso prodotti pulizia. Indirizzo esatto filiale, telefono ed email non reperiti con certezza. [DUPLICATO — vedi anche: 2026-08-31_08_Italia_Toscana_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Via Oreto 34, 98100 Messina (fonte ufficiale; lista grezza indicava 'Via Oreto 1', non confermato). Stessa realta/gruppo della filiale di Palermo, tenuta come riga separata per provincia diversa.</t>
+          <t>Via Oreto 34, 98100 Messina (fonte ufficiale; lista grezza indicava 'Via Oreto 1', non confermato). Stessa realta/gruppo della filiale di Palermo, tenuta come riga separata per provincia diversa. [DUPLICATO — vedi anche: 2026-08-31_08_Italia_Toscana_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
